--- a/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
+++ b/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0767FA4-B6B7-4FC0-9698-1616BB0B360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAF7224-2380-4FBB-9BA2-848C724749FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <author>tc={AFE4F70E-4F68-4601-B8CF-DFA896FC8A62}</author>
     <author>tc={50E20A73-76EE-480B-AC2B-85B9568229B3}</author>
     <author>tc={A66B6FDD-7E3A-402B-8E6B-7073C79B9436}</author>
-    <author>tc={5F7F21A6-9267-43AB-9E2F-857C43A6B051}</author>
-    <author>tc={87F94307-F9C1-413A-A184-19A69689A8AF}</author>
-    <author>tc={011C4874-472E-423F-9F9E-1A44747EBF50}</author>
     <author>tc={F7866A31-18E0-48C6-B567-67C836D4C8B7}</author>
     <author>Timon Geiß</author>
     <author>tc={24965C23-66A2-443D-B1F3-FDFF8EFF87E6}</author>
@@ -74,31 +71,7 @@
     0,7 * 10^6 /1000 </t>
       </text>
     </comment>
-    <comment ref="E23" authorId="3" shapeId="0" xr:uid="{5F7F21A6-9267-43AB-9E2F-857C43A6B051}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    1750 kWh_th/t durch 1000</t>
-      </text>
-    </comment>
-    <comment ref="E24" authorId="4" shapeId="0" xr:uid="{87F94307-F9C1-413A-A184-19A69689A8AF}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    800 €/t*a * 8760 h/a / 1000 kg/t = €/kg *h</t>
-      </text>
-    </comment>
-    <comment ref="E25" authorId="5" shapeId="0" xr:uid="{011C4874-472E-423F-9F9E-1A44747EBF50}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    ~ 40 opex/ 800 capex</t>
-      </text>
-    </comment>
-    <comment ref="E39" authorId="6" shapeId="0" xr:uid="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
+    <comment ref="E42" authorId="3" shapeId="0" xr:uid="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
       <text>
         <t>[Kommentarthread]
 Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -112,7 +85,7 @@
     55 % pro Monat --&gt; /31 = 1,77 %/d --&gt; / 24 = 0,074 %/h</t>
       </text>
     </comment>
-    <comment ref="E49" authorId="7" shapeId="0" xr:uid="{22946658-3822-4C9A-8007-CC034FA9B8AB}">
+    <comment ref="E52" authorId="4" shapeId="0" xr:uid="{22946658-3822-4C9A-8007-CC034FA9B8AB}">
       <text>
         <r>
           <rPr>
@@ -136,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E50" authorId="7" shapeId="0" xr:uid="{426A9046-86EB-4AF9-8A2D-1FEFC7B6C4A3}">
+    <comment ref="E53" authorId="4" shapeId="0" xr:uid="{426A9046-86EB-4AF9-8A2D-1FEFC7B6C4A3}">
       <text>
         <r>
           <rPr>
@@ -160,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="7" shapeId="0" xr:uid="{360FC6EE-8AD3-4EF7-B2BF-00DD1029DCAF}">
+    <comment ref="E54" authorId="4" shapeId="0" xr:uid="{360FC6EE-8AD3-4EF7-B2BF-00DD1029DCAF}">
       <text>
         <r>
           <rPr>
@@ -184,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E73" authorId="8" shapeId="0" xr:uid="{24965C23-66A2-443D-B1F3-FDFF8EFF87E6}">
+    <comment ref="E76" authorId="5" shapeId="0" xr:uid="{24965C23-66A2-443D-B1F3-FDFF8EFF87E6}">
       <text>
         <t>[Kommentarthread]
 Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -197,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="382">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -894,9 +867,6 @@
     <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
-    <t>CO2-Bereitstellung / Direct Air Capture</t>
-  </si>
-  <si>
     <t>Methanolsynthese</t>
   </si>
   <si>
@@ -936,21 +906,6 @@
     <t>kg_CO2/kg_CH3OH</t>
   </si>
   <si>
-    <t>strombedarf_dac</t>
-  </si>
-  <si>
-    <t>capex_dac</t>
-  </si>
-  <si>
-    <t>opex_dac</t>
-  </si>
-  <si>
-    <t>lebensdauer_dac</t>
-  </si>
-  <si>
-    <t>zinssatz_dac</t>
-  </si>
-  <si>
     <t>kWh/kg_CO2</t>
   </si>
   <si>
@@ -999,30 +954,6 @@
     <t>kg_CO2/a</t>
   </si>
   <si>
-    <t>annuity_dac</t>
-  </si>
-  <si>
-    <t>result_dac_leistung</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_elin</t>
-  </si>
-  <si>
-    <t>calc_gesamtinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_opex_fix_dac</t>
-  </si>
-  <si>
-    <t>calc_annuity_dac</t>
-  </si>
-  <si>
-    <t>calc_verzinstinvest_dac</t>
-  </si>
-  <si>
-    <t>calc_cost_dac</t>
-  </si>
-  <si>
     <t>Kohlendioxidproduktion</t>
   </si>
   <si>
@@ -1044,9 +975,6 @@
     <t>Levelized Cost of Carbon</t>
   </si>
   <si>
-    <t>calc_lcon_dac</t>
-  </si>
-  <si>
     <t>calc_lcof_ms</t>
   </si>
   <si>
@@ -1098,9 +1026,6 @@
     <t>Wärmebedarf</t>
   </si>
   <si>
-    <t>waerme_bedarf_dac</t>
-  </si>
-  <si>
     <t>kWh_th/kg_CO2</t>
   </si>
   <si>
@@ -1143,12 +1068,6 @@
     <t>MWh_el/a</t>
   </si>
   <si>
-    <t>result_dac_flowsum_co2out</t>
-  </si>
-  <si>
-    <t>result_dac_flowsum_qin</t>
-  </si>
-  <si>
     <t>result_ms_flowsum_ch3ohout</t>
   </si>
   <si>
@@ -1306,6 +1225,99 @@
   </si>
   <si>
     <t>calc_biogasbezug_kosten</t>
+  </si>
+  <si>
+    <t>strombedarf_mea</t>
+  </si>
+  <si>
+    <t>waerme_bedarf_mea</t>
+  </si>
+  <si>
+    <t>capex_mea</t>
+  </si>
+  <si>
+    <t>opex_mea</t>
+  </si>
+  <si>
+    <t>MEA (Lösungsmittel) Bedarf</t>
+  </si>
+  <si>
+    <t>mittelbedarf_mea</t>
+  </si>
+  <si>
+    <t>kg_MEA/kg_CO2</t>
+  </si>
+  <si>
+    <t>lebensdauer_mea</t>
+  </si>
+  <si>
+    <t>zinssatz_mea</t>
+  </si>
+  <si>
+    <t>CO2-Bereitstellung / Industriegasabscheidung MEA</t>
+  </si>
+  <si>
+    <t>annuity_mea</t>
+  </si>
+  <si>
+    <t>result_mea_leistung</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_elin</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_co2out</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_qin</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_mea</t>
+  </si>
+  <si>
+    <t>calc_annuity_mea</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_mea</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_mea</t>
+  </si>
+  <si>
+    <t>calc_cost_mea</t>
+  </si>
+  <si>
+    <t>calc_lcon_mea</t>
+  </si>
+  <si>
+    <t>Biogasbedarf</t>
+  </si>
+  <si>
+    <t>biogasbedarf_mea</t>
+  </si>
+  <si>
+    <t>kg_biogas/kg_CO2</t>
+  </si>
+  <si>
+    <t>result_mea_flowsum_biogasin</t>
+  </si>
+  <si>
+    <t>kg_Biogas/a</t>
+  </si>
+  <si>
+    <t>mittelkosten_mea</t>
+  </si>
+  <si>
+    <t>€/kg_CO2</t>
+  </si>
+  <si>
+    <t>OPEX Fix</t>
+  </si>
+  <si>
+    <t>MEA (Lösungsmittel) Kosten OPEX var</t>
+  </si>
+  <si>
+    <t>calc_opex_var_mea</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1330,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1374,6 +1386,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1384,7 +1403,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1471,7 +1490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1501,6 +1520,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1508,6 +1549,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1544,27 +1588,8 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1862,27 +1887,18 @@
   <threadedComment ref="E18" dT="2025-03-18T08:08:24.46" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{A66B6FDD-7E3A-402B-8E6B-7073C79B9436}">
     <text xml:space="preserve">0,7 * 10^6 /1000 </text>
   </threadedComment>
-  <threadedComment ref="E23" dT="2025-03-18T08:05:52.08" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{5F7F21A6-9267-43AB-9E2F-857C43A6B051}">
-    <text>1750 kWh_th/t durch 1000</text>
-  </threadedComment>
-  <threadedComment ref="E24" dT="2025-03-14T09:24:29.74" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{87F94307-F9C1-413A-A184-19A69689A8AF}">
-    <text>800 €/t*a * 8760 h/a / 1000 kg/t = €/kg *h</text>
-  </threadedComment>
-  <threadedComment ref="E25" dT="2025-03-14T09:25:24.78" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{011C4874-472E-423F-9F9E-1A44747EBF50}">
-    <text>~ 40 opex/ 800 capex</text>
-  </threadedComment>
-  <threadedComment ref="E39" dT="2025-03-26T10:22:08.04" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
+  <threadedComment ref="E42" dT="2025-03-26T10:22:08.04" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
     <text>Wochenfaktor 4,33 * 24h *7d = 727,44h/monat
 4,55 %/monat * 1/727,44 monat/h</text>
   </threadedComment>
-  <threadedComment ref="E39" dT="2025-03-26T10:28:05.27" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{02E78AB9-E14B-4034-A3AB-3EF5F06F95CB}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
+  <threadedComment ref="E42" dT="2025-03-26T10:28:05.27" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{02E78AB9-E14B-4034-A3AB-3EF5F06F95CB}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
     <text>Wochenfaktor 4,33 * 24h * 7d= 727,44 h/monat
 4,55 %/monat * 1/727 monat/h</text>
   </threadedComment>
-  <threadedComment ref="E39" dT="2025-04-02T11:01:30.13" personId="{1C9DF23A-CC4A-4BFD-AF20-2D2787398686}" id="{7A1231DE-7CE0-49C4-BF40-EE9EE75E0E1A}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
+  <threadedComment ref="E42" dT="2025-04-02T11:01:30.13" personId="{1C9DF23A-CC4A-4BFD-AF20-2D2787398686}" id="{7A1231DE-7CE0-49C4-BF40-EE9EE75E0E1A}" parentId="{F7866A31-18E0-48C6-B567-67C836D4C8B7}">
     <text>55 % pro Monat --&gt; /31 = 1,77 %/d --&gt; / 24 = 0,074 %/h</text>
   </threadedComment>
-  <threadedComment ref="E73" dT="2025-03-18T07:43:27.70" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{24965C23-66A2-443D-B1F3-FDFF8EFF87E6}">
+  <threadedComment ref="E76" dT="2025-03-18T07:43:27.70" personId="{7B1A26D8-2D09-4CF3-BDB9-5A9185883024}" id="{24965C23-66A2-443D-B1F3-FDFF8EFF87E6}">
     <text>https://de.statista.com/statistik/daten/studie/730823/umfrage/durchschnittlicher-preis-fuer-methanol-auf-dem-europaeischen-markt/</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1896,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
@@ -1935,10 +1951,10 @@
       <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1955,8 +1971,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
@@ -1971,8 +1987,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="35"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1987,8 +2003,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="35"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2003,8 +2019,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="35"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2019,8 +2035,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2035,31 +2051,31 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="38" t="s">
-        <v>232</v>
+      <c r="A8" s="46"/>
+      <c r="B8" s="57" t="s">
+        <v>231</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E8" s="12">
         <v>1.5</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="35"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E9" s="7">
         <v>285.39999999999998</v>
@@ -2069,29 +2085,29 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E10" s="7">
         <v>5000</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="35"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E11" s="9">
         <v>0.05</v>
@@ -2101,45 +2117,45 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="35"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E12" s="7">
         <v>0.189</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="46"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="E13" s="7">
         <v>1.375</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="35"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E14" s="10">
         <v>25</v>
@@ -2149,13 +2165,13 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="39"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E15" s="14">
         <v>0.08</v>
@@ -2165,15 +2181,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="38" t="s">
-        <v>288</v>
+      <c r="A16" s="46"/>
+      <c r="B16" s="57" t="s">
+        <v>273</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E16" s="16">
         <v>3.7</v>
@@ -2183,45 +2199,45 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="35"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E17" s="9">
         <v>0.27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="35"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="E18" s="9">
         <v>700</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="35"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E19" s="9">
         <v>0.02</v>
@@ -2231,13 +2247,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="35"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="E20" s="9">
         <v>20</v>
@@ -2247,13 +2263,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="39"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="E21" s="14">
         <v>0.05</v>
@@ -2263,883 +2279,931 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="40" t="s">
-        <v>360</v>
+      <c r="A22" s="46"/>
+      <c r="B22" s="59" t="s">
+        <v>342</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.5</v>
+      <c r="D22" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="E22" s="39">
+        <v>0.2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="46"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.75</v>
+        <v>283</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="39">
+        <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="46"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" s="7">
-        <v>7000</v>
+      <c r="D24" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="E24" s="39">
+        <v>1640</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="40"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.05</v>
+        <v>379</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="E25" s="41">
+        <v>0.04</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="40"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="E26" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>356</v>
+      </c>
+      <c r="E27" s="43">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="E28" s="43">
+        <v>1.5E-3</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="46"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" s="10">
+      <c r="D29" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="E29" s="44">
+        <v>25</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="46"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="D30" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="E30" s="41">
+        <v>0.08</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="15">
+        <v>490</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="46"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="46"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="10">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="28"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="1" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="46"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="23">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="46"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="46"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="46"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="46"/>
+      <c r="B39" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="15">
-        <v>490</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="1" t="s">
+      <c r="D39" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E39" s="15">
+        <v>2.83</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="46"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="1" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="46"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="10">
+      <c r="D41" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E41" s="10">
+        <v>30</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="46"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E42" s="9">
+        <v>7.3999999999999999E-4</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="46"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="46"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.98</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="46"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="46"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="46"/>
+      <c r="B47" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="16">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="46"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="7">
+        <f>E49*4</f>
+        <v>424</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="46"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="7">
+        <v>106</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="46"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="46"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="46"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="46"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="46"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="46"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="10">
+        <v>15</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="23">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="F32" s="1" t="s">
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="47"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="F56" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="F33" s="1" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="32">
+        <v>0.1699</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="48"/>
+      <c r="B58" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="29">
+        <v>0</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="46"/>
+      <c r="B59" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="16">
+        <v>0.99</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="46"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="19">
+        <v>1100</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="46"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="19">
+        <v>17.84</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="46"/>
+      <c r="B62" s="50"/>
+      <c r="C62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="46"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="10">
+        <v>25</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="46"/>
+      <c r="B64" s="50"/>
+      <c r="C64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="46"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="14">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F65" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="1" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="46"/>
+      <c r="B66" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="16">
+        <v>0.997</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="46"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="19">
+        <v>1080</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="46"/>
+      <c r="B68" s="50"/>
+      <c r="C68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" s="19">
+        <v>12.68</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="46"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="21">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="46"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70" s="10">
+        <v>25</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="46"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E71" s="20">
+        <v>1000000</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="47"/>
+      <c r="B72" s="53"/>
+      <c r="C72" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="D72" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E72" s="18">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="F72" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="28"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="14">
-        <v>0</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E36" s="15">
-        <v>2.83</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="10">
-        <v>30</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E39" s="9">
-        <v>7.3999999999999999E-4</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.98</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="28"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.98</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="28"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="28"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="E43" s="14">
-        <v>0</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="28"/>
-      <c r="B44" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="16">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="28"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="7">
-        <f>E46*4</f>
-        <v>424</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="28"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="7">
-        <v>106</v>
-      </c>
-      <c r="F46" s="1" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="35">
+        <v>-1E-4</v>
+      </c>
+      <c r="F73" s="34" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="28"/>
-      <c r="B48" s="35"/>
-      <c r="C48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="28"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="9">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="10">
-        <v>15</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="29"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="D54" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" s="47">
-        <v>0.1699</v>
-      </c>
-      <c r="F54" s="46" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="46"/>
+      <c r="B74" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-1E-4</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="41"/>
-      <c r="B55" s="42" t="s">
-        <v>361</v>
-      </c>
-      <c r="C55" s="43" t="s">
-        <v>362</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>363</v>
-      </c>
-      <c r="E55" s="44">
-        <v>0</v>
-      </c>
-      <c r="F55" s="43" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="28"/>
-      <c r="B56" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="16">
-        <v>0.99</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="19">
-        <v>1100</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="28"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" s="19">
-        <v>17.84</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E60" s="10">
-        <v>25</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="28"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E61" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="28"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62" s="14">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="28"/>
-      <c r="B63" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="16">
-        <v>0.997</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="19">
-        <v>1080</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="28"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E65" s="19">
-        <v>12.68</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="28"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="21">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="28"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="10">
-        <v>25</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="28"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E68" s="20">
-        <v>1000000</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="29"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="18">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="D70" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="50">
-        <v>-1E-4</v>
-      </c>
-      <c r="F70" s="49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="28"/>
-      <c r="B71" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-1E-4</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="28"/>
-      <c r="B72" s="24" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="46"/>
+      <c r="B75" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="25" t="s">
+      <c r="C75" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="25" t="s">
+      <c r="D75" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E72" s="26">
+      <c r="E75" s="26">
         <v>-1.5</v>
       </c>
-      <c r="F72" s="25" t="s">
+      <c r="F75" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="29"/>
-      <c r="B73" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="E73" s="18">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="47"/>
+      <c r="B76" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="E76" s="18">
         <v>-0.6</v>
       </c>
-      <c r="F73" s="17" t="s">
-        <v>290</v>
+      <c r="F76" s="17" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:A27"/>
-    <mergeCell ref="A28:A53"/>
-    <mergeCell ref="A54:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="B63:B69"/>
-    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="A2:A30"/>
+    <mergeCell ref="A31:A56"/>
+    <mergeCell ref="A57:A72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="B31:B38"/>
+    <mergeCell ref="B59:B65"/>
+    <mergeCell ref="B66:B72"/>
+    <mergeCell ref="B47:B56"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="B8:B15"/>
-    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B22:B30"/>
     <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B36:B43"/>
+    <mergeCell ref="B39:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3149,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
@@ -3182,10 +3246,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3200,8 +3264,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
         <v>108</v>
       </c>
@@ -3214,8 +3278,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="35"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
@@ -3228,8 +3292,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="35"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="1" t="s">
         <v>139</v>
       </c>
@@ -3242,8 +3306,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="35"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="1" t="s">
         <v>142</v>
       </c>
@@ -3256,8 +3320,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="1" t="s">
         <v>156</v>
       </c>
@@ -3270,8 +3334,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="35"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="1" t="s">
         <v>198</v>
       </c>
@@ -3284,8 +3348,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="35"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="1" t="s">
         <v>168</v>
       </c>
@@ -3298,8 +3362,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="35"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="1" t="s">
         <v>190</v>
       </c>
@@ -3312,20 +3376,20 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="35"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="54"/>
       <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="38" t="s">
-        <v>232</v>
+      <c r="A12" s="46"/>
+      <c r="B12" s="57" t="s">
+        <v>231</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="11" t="s">
@@ -3333,27 +3397,27 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="35"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="35"/>
+      <c r="A14" s="46"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
@@ -3361,27 +3425,27 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="35"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="35"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="1" t="s">
@@ -3389,13 +3453,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="35"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="1" t="s">
@@ -3403,13 +3467,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="35"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="1" t="s">
@@ -3417,13 +3481,13 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="35"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="1" t="s">
@@ -3431,13 +3495,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="35"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="1" t="s">
@@ -3445,13 +3509,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="35"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="1" t="s">
         <v>190</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="1" t="s">
@@ -3459,37 +3523,37 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="39"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="14"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="38" t="s">
-        <v>288</v>
+      <c r="A23" s="46"/>
+      <c r="B23" s="57" t="s">
+        <v>273</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="1" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="35"/>
+      <c r="A24" s="46"/>
+      <c r="B24" s="54"/>
       <c r="C24" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="1" t="s">
@@ -3497,41 +3561,41 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="35"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="1" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="35"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="54"/>
       <c r="C26" s="1" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="1" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="35"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="1" t="s">
@@ -3539,13 +3603,13 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="35"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="1" t="s">
@@ -3553,13 +3617,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="35"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="1" t="s">
@@ -3567,13 +3631,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="35"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="1" t="s">
         <v>168</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="1" t="s">
@@ -3581,13 +3645,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="1" t="s">
         <v>190</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="1" t="s">
@@ -3595,23 +3659,23 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="39"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
       <c r="E32" s="14"/>
       <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="31" t="s">
-        <v>231</v>
+      <c r="A33" s="46"/>
+      <c r="B33" s="59" t="s">
+        <v>360</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="1" t="s">
@@ -3619,13 +3683,13 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="31"/>
+      <c r="A34" s="46"/>
+      <c r="B34" s="59"/>
       <c r="C34" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="1" t="s">
@@ -3633,13 +3697,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="31"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="59"/>
       <c r="C35" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>268</v>
+        <v>363</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="1" t="s">
@@ -3647,69 +3711,69 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="31"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="1" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="1" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="31"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="1" t="s">
-        <v>274</v>
+        <v>372</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E37" s="10"/>
+        <v>375</v>
+      </c>
+      <c r="E37" s="9"/>
       <c r="F37" s="1" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="31"/>
+      <c r="A38" s="46"/>
+      <c r="B38" s="59"/>
       <c r="C38" s="1" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>269</v>
+        <v>364</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="1" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="31"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="59"/>
       <c r="C39" s="1" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>270</v>
+        <v>366</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="31"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="59"/>
       <c r="C40" s="1" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="1" t="s">
@@ -3717,162 +3781,162 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="28"/>
-      <c r="B41" s="31"/>
+      <c r="A41" s="46"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E41" s="9"/>
+        <v>381</v>
+      </c>
+      <c r="E41" s="10"/>
       <c r="F41" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="28"/>
-      <c r="B42" s="31"/>
+      <c r="A42" s="46"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E42" s="9"/>
+        <v>367</v>
+      </c>
+      <c r="E42" s="10"/>
       <c r="F42" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="28"/>
-      <c r="B43" s="31"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="46"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>368</v>
+      </c>
       <c r="E43" s="9"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="27" t="s">
+      <c r="F43" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="46"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="46"/>
+      <c r="B45" s="59"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B46" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="2" t="s">
+      <c r="E46" s="15"/>
+      <c r="F46" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="28"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="1" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="46"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="28"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="46"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="28"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="28"/>
-      <c r="B49" s="31"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="50"/>
       <c r="C49" s="1" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
-      <c r="B50" s="31"/>
+      <c r="A50" s="46"/>
+      <c r="B50" s="50"/>
       <c r="C50" s="1" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="31"/>
+      <c r="A51" s="46"/>
+      <c r="B51" s="50"/>
       <c r="C51" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
-      <c r="B52" s="31"/>
+      <c r="A52" s="46"/>
+      <c r="B52" s="50"/>
       <c r="C52" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="1" t="s">
@@ -3880,135 +3944,135 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="13"/>
+      <c r="A53" s="46"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" s="9"/>
+      <c r="F53" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="28"/>
-      <c r="B54" s="31" t="s">
-        <v>335</v>
-      </c>
+      <c r="A54" s="46"/>
+      <c r="B54" s="50"/>
       <c r="C54" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="46"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="13"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="46"/>
+      <c r="B56" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="28"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="1" t="s">
+      <c r="D56" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="46"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="28"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="E57" s="9"/>
       <c r="F57" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="46"/>
+      <c r="B58" s="50"/>
+      <c r="C58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="28"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="31"/>
+      <c r="A59" s="46"/>
+      <c r="B59" s="50"/>
       <c r="C59" s="1" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="31"/>
+      <c r="A60" s="46"/>
+      <c r="B60" s="50"/>
       <c r="C60" s="1" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="28"/>
-      <c r="B61" s="31"/>
+      <c r="A61" s="46"/>
+      <c r="B61" s="50"/>
       <c r="C61" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="E61" s="9"/>
       <c r="F61" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="28"/>
-      <c r="B62" s="31"/>
+      <c r="A62" s="46"/>
+      <c r="B62" s="50"/>
       <c r="C62" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="E62" s="9"/>
       <c r="F62" s="1" t="s">
@@ -4016,1072 +4080,1100 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="28"/>
-      <c r="B63" s="32"/>
+      <c r="A63" s="46"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="E63" s="9"/>
+      <c r="F63" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="33" t="s">
+      <c r="A64" s="46"/>
+      <c r="B64" s="50"/>
+      <c r="C64" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E64" s="9"/>
+      <c r="F64" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="46"/>
+      <c r="B65" s="51"/>
+      <c r="E65" s="9"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="46"/>
+      <c r="B66" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C66" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="11" t="s">
+      <c r="E66" s="16"/>
+      <c r="F66" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="28"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="1" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="46"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="1" t="s">
+      <c r="E67" s="9"/>
+      <c r="F67" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="28"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="1" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="46"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="28"/>
-      <c r="B67" s="35"/>
-      <c r="C67" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="28"/>
-      <c r="B68" s="35"/>
-      <c r="C68" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
-      <c r="B69" s="35"/>
+      <c r="A69" s="46"/>
+      <c r="B69" s="54"/>
       <c r="C69" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" s="9"/>
+        <v>186</v>
+      </c>
+      <c r="E69" s="7"/>
       <c r="F69" s="1" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="28"/>
-      <c r="B70" s="35"/>
+      <c r="A70" s="46"/>
+      <c r="B70" s="54"/>
       <c r="C70" s="1" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="1" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="28"/>
-      <c r="B71" s="35"/>
+      <c r="A71" s="46"/>
+      <c r="B71" s="54"/>
       <c r="C71" s="1" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="E71" s="9"/>
       <c r="F71" s="1" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="28"/>
-      <c r="B72" s="35"/>
+      <c r="A72" s="46"/>
+      <c r="B72" s="54"/>
       <c r="C72" s="1" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="E72" s="7"/>
       <c r="F72" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="28"/>
-      <c r="B73" s="35"/>
+      <c r="A73" s="46"/>
+      <c r="B73" s="54"/>
       <c r="C73" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E73" s="9"/>
       <c r="F73" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="28"/>
-      <c r="B74" s="35"/>
+      <c r="A74" s="46"/>
+      <c r="B74" s="54"/>
       <c r="C74" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E74" s="9"/>
       <c r="F74" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="29"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="17"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="46"/>
+      <c r="B75" s="54"/>
+      <c r="C75" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="46"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="47"/>
+      <c r="B77" s="55"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="17"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="37" t="s">
+      <c r="B78" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="2" t="s">
+      <c r="E78" s="15"/>
+      <c r="F78" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="28"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="52" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="46"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="D77" s="52" t="s">
+      <c r="D79" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="E77" s="53"/>
-      <c r="F77" s="52" t="s">
+      <c r="E79" s="37"/>
+      <c r="F79" s="36" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="28"/>
-      <c r="B78" s="39"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="13"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="28"/>
-      <c r="B79" s="51" t="s">
-        <v>361</v>
-      </c>
-      <c r="C79" s="52" t="s">
-        <v>364</v>
-      </c>
-      <c r="D79" s="52" t="s">
-        <v>367</v>
-      </c>
-      <c r="E79" s="53"/>
-      <c r="F79" s="52" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="28"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="1" t="s">
+      <c r="A80" s="46"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="13"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="46"/>
+      <c r="B81" s="60" t="s">
+        <v>343</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>346</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="E81" s="37"/>
+      <c r="F81" s="36" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="46"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E82" s="7"/>
+      <c r="F82" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="28"/>
-      <c r="B81" s="51"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="28"/>
-      <c r="B82" s="33" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="46"/>
+      <c r="B83" s="60"/>
+      <c r="E83" s="7"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="46"/>
+      <c r="B84" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C84" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="D84" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E82" s="16"/>
-      <c r="F82" s="11" t="s">
+      <c r="E84" s="16"/>
+      <c r="F84" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="28"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="1" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="46"/>
+      <c r="B85" s="50"/>
+      <c r="C85" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E83" s="19"/>
-      <c r="F83" s="1" t="s">
+      <c r="E85" s="19"/>
+      <c r="F85" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="28"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="1" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="46"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E84" s="19"/>
-      <c r="F84" s="1" t="s">
+      <c r="E86" s="19"/>
+      <c r="F86" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="28"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="1" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="46"/>
+      <c r="B87" s="50"/>
+      <c r="C87" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="28"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" s="10"/>
-      <c r="F86" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="28"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="28"/>
-      <c r="B88" s="31"/>
+      <c r="A88" s="46"/>
+      <c r="B88" s="50"/>
       <c r="C88" s="1" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E88" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="E88" s="10"/>
       <c r="F88" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="28"/>
-      <c r="B89" s="31"/>
+      <c r="A89" s="46"/>
+      <c r="B89" s="50"/>
       <c r="C89" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E89" s="9"/>
+        <v>163</v>
+      </c>
+      <c r="E89" s="7"/>
       <c r="F89" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="28"/>
-      <c r="B90" s="31"/>
+      <c r="A90" s="46"/>
+      <c r="B90" s="50"/>
       <c r="C90" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E90" s="9"/>
+        <v>200</v>
+      </c>
+      <c r="E90" s="7"/>
       <c r="F90" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="28"/>
-      <c r="B91" s="32"/>
+      <c r="A91" s="46"/>
+      <c r="B91" s="50"/>
+      <c r="C91" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="28"/>
-      <c r="B92" s="33" t="s">
+      <c r="A92" s="46"/>
+      <c r="B92" s="50"/>
+      <c r="C92" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="46"/>
+      <c r="B93" s="51"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="46"/>
+      <c r="B94" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C94" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D94" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="11" t="s">
+      <c r="E94" s="16"/>
+      <c r="F94" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="28"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="1" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="46"/>
+      <c r="B95" s="50"/>
+      <c r="C95" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="E93" s="19"/>
-      <c r="F93" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="28"/>
-      <c r="B94" s="31"/>
-      <c r="C94" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E94" s="19"/>
-      <c r="F94" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="28"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="E95" s="19"/>
       <c r="F95" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="46"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E96" s="19"/>
+      <c r="F96" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="46"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E97" s="19"/>
+      <c r="F97" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="28"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="1" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="46"/>
+      <c r="B98" s="50"/>
+      <c r="C98" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E96" s="10"/>
-      <c r="F96" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="28"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E97" s="20"/>
-      <c r="F97" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="28"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E98" s="20"/>
+      <c r="E98" s="10"/>
       <c r="F98" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="28"/>
-      <c r="B99" s="31"/>
+      <c r="A99" s="46"/>
+      <c r="B99" s="50"/>
       <c r="C99" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E99" s="9"/>
+        <v>161</v>
+      </c>
+      <c r="E99" s="20"/>
       <c r="F99" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="28"/>
-      <c r="B100" s="31"/>
+      <c r="A100" s="46"/>
+      <c r="B100" s="50"/>
       <c r="C100" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E100" s="9"/>
+        <v>199</v>
+      </c>
+      <c r="E100" s="20"/>
       <c r="F100" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="29"/>
-      <c r="B101" s="34"/>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="46"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E101" s="9"/>
+      <c r="F101" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="27" t="s">
+      <c r="A102" s="46"/>
+      <c r="B102" s="50"/>
+      <c r="C102" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E102" s="9"/>
+      <c r="F102" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="47"/>
+      <c r="B103" s="53"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="B102" s="37" t="s">
+      <c r="B104" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="2" t="s">
+      <c r="E104" s="6"/>
+      <c r="F104" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="28"/>
-      <c r="B103" s="35"/>
-      <c r="C103" s="1" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="46"/>
+      <c r="B105" s="54"/>
+      <c r="C105" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E103" s="9"/>
-      <c r="F103" s="1" t="s">
+      <c r="E105" s="9"/>
+      <c r="F105" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="28"/>
-      <c r="B104" s="35"/>
-      <c r="C104" s="1" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="46"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="E104" s="9"/>
-      <c r="F104" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="28"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="13"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="28"/>
-      <c r="B106" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="1" t="s">
-        <v>310</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="28"/>
-      <c r="B107" s="35"/>
-      <c r="C107" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E107" s="9"/>
-      <c r="F107" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="A107" s="46"/>
+      <c r="B107" s="58"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="13"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="28"/>
-      <c r="B108" s="35"/>
+      <c r="A108" s="46"/>
+      <c r="B108" s="57" t="s">
+        <v>303</v>
+      </c>
       <c r="C108" s="1" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="E108" s="9"/>
       <c r="F108" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="46"/>
+      <c r="B109" s="54"/>
+      <c r="C109" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E109" s="9"/>
+      <c r="F109" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="28"/>
-      <c r="B109" s="39"/>
-      <c r="E109" s="9"/>
-    </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="28"/>
-      <c r="B110" s="38" t="s">
+      <c r="A110" s="46"/>
+      <c r="B110" s="54"/>
+      <c r="C110" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E110" s="9"/>
+      <c r="F110" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="46"/>
+      <c r="B111" s="58"/>
+      <c r="E111" s="9"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="46"/>
+      <c r="B112" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D112" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="E110" s="16"/>
-      <c r="F110" s="11" t="s">
+      <c r="E112" s="16"/>
+      <c r="F112" s="11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="28"/>
-      <c r="B111" s="35"/>
-      <c r="C111" s="1" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="46"/>
+      <c r="B113" s="54"/>
+      <c r="C113" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="28"/>
-      <c r="B112" s="39"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="14"/>
-      <c r="F112" s="13"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="28"/>
-      <c r="B113" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="E113" s="9"/>
       <c r="F113" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="46"/>
+      <c r="B114" s="58"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="13"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="46"/>
+      <c r="B115" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="28"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E114" s="9"/>
-      <c r="F114" s="1" t="s">
+      <c r="E115" s="9"/>
+      <c r="F115" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="46"/>
+      <c r="B116" s="54"/>
+      <c r="C116" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E116" s="9"/>
+      <c r="F116" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="29"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="17"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="27" t="s">
+    <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="47"/>
+      <c r="B117" s="55"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="17"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="B116" s="37" t="s">
+      <c r="B118" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D118" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2" t="s">
+      <c r="E118" s="2"/>
+      <c r="F118" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="28"/>
-      <c r="B117" s="35"/>
-      <c r="C117" s="1" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="46"/>
+      <c r="B119" s="54"/>
+      <c r="C119" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="28"/>
-      <c r="B118" s="39"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="28"/>
-      <c r="B119" s="38" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="46"/>
+      <c r="B120" s="58"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="46"/>
+      <c r="B121" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="28"/>
-      <c r="B120" s="35"/>
-      <c r="C120" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="28"/>
-      <c r="B121" s="35"/>
-      <c r="C121" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="28"/>
-      <c r="B122" s="35"/>
+      <c r="A122" s="46"/>
+      <c r="B122" s="54"/>
       <c r="C122" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>179</v>
+        <v>311</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="28"/>
-      <c r="B123" s="35"/>
+      <c r="A123" s="46"/>
+      <c r="B123" s="54"/>
       <c r="C123" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="28"/>
-      <c r="B124" s="35"/>
+      <c r="A124" s="46"/>
+      <c r="B124" s="54"/>
       <c r="C124" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="28"/>
-      <c r="B125" s="35"/>
+      <c r="A125" s="46"/>
+      <c r="B125" s="54"/>
+      <c r="C125" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="28"/>
-      <c r="B126" s="38" t="s">
+      <c r="A126" s="46"/>
+      <c r="B126" s="54"/>
+      <c r="C126" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="46"/>
+      <c r="B127" s="54"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="46"/>
+      <c r="B128" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C128" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11" t="s">
+      <c r="E128" s="11"/>
+      <c r="F128" s="11" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="28"/>
-      <c r="B127" s="35"/>
-      <c r="C127" s="1" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="46"/>
+      <c r="B129" s="54"/>
+      <c r="C129" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="28"/>
-      <c r="B128" s="35"/>
-      <c r="C128" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="28"/>
-      <c r="B129" s="35"/>
-      <c r="C129" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="28"/>
-      <c r="B130" s="35"/>
+      <c r="A130" s="46"/>
+      <c r="B130" s="54"/>
       <c r="C130" s="1" t="s">
-        <v>330</v>
+        <v>217</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>331</v>
+        <v>216</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>334</v>
+        <v>221</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="28"/>
-      <c r="B131" s="35"/>
+      <c r="A131" s="46"/>
+      <c r="B131" s="54"/>
       <c r="C131" s="1" t="s">
-        <v>354</v>
+        <v>207</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>355</v>
+        <v>211</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>334</v>
+        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="28"/>
-      <c r="B132" s="35"/>
+      <c r="A132" s="46"/>
+      <c r="B132" s="54"/>
       <c r="C132" s="1" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="28"/>
-      <c r="B133" s="35"/>
+      <c r="A133" s="46"/>
+      <c r="B133" s="54"/>
       <c r="C133" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="46"/>
+      <c r="B134" s="54"/>
+      <c r="C134" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="46"/>
+      <c r="B135" s="54"/>
+      <c r="C135" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="28"/>
-      <c r="B134" s="35"/>
-      <c r="C134" s="1" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="46"/>
+      <c r="B136" s="54"/>
+      <c r="C136" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="28"/>
-      <c r="B135" s="35"/>
-      <c r="C135" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="28"/>
-      <c r="B136" s="35"/>
-      <c r="C136" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="28"/>
-      <c r="B137" s="35"/>
+      <c r="A137" s="46"/>
+      <c r="B137" s="54"/>
       <c r="C137" s="1" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="F137" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="46"/>
+      <c r="B138" s="54"/>
+      <c r="C138" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="46"/>
+      <c r="B139" s="54"/>
+      <c r="C139" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="28"/>
-      <c r="B138" s="35"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="28"/>
-      <c r="B139" s="38" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="46"/>
+      <c r="B140" s="54"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="46"/>
+      <c r="B141" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="C139" s="11" t="s">
+      <c r="C141" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D139" s="11" t="s">
+      <c r="D141" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11" t="s">
+      <c r="E141" s="11"/>
+      <c r="F141" s="11" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="28"/>
-      <c r="B140" s="35"/>
-      <c r="C140" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="28"/>
-      <c r="B141" s="35"/>
-      <c r="C141" s="1" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="46"/>
+      <c r="B142" s="54"/>
+      <c r="C142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="46"/>
+      <c r="B143" s="54"/>
+      <c r="C143" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="28"/>
-      <c r="B142" s="35"/>
-      <c r="C142" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F142" s="1" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="46"/>
+      <c r="B144" s="54"/>
+      <c r="C144" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="28"/>
-      <c r="B143" s="35"/>
-      <c r="C143" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F143" s="1" t="s">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="46"/>
+      <c r="B145" s="54"/>
+      <c r="C145" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>215</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B119:B125"/>
-    <mergeCell ref="B139:B143"/>
-    <mergeCell ref="A116:A143"/>
-    <mergeCell ref="B126:B138"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="A76:A101"/>
-    <mergeCell ref="B82:B91"/>
-    <mergeCell ref="B92:B101"/>
-    <mergeCell ref="A102:A115"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B121:B127"/>
+    <mergeCell ref="B141:B145"/>
+    <mergeCell ref="A118:A145"/>
+    <mergeCell ref="B128:B140"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B33:B45"/>
+    <mergeCell ref="A46:A77"/>
+    <mergeCell ref="B66:B77"/>
     <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="B56:B65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
+++ b/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAF7224-2380-4FBB-9BA2-848C724749FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDE88E2-6357-429F-8770-CEB1ACFB89C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="387">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1318,6 +1318,21 @@
   </si>
   <si>
     <t>calc_opex_var_mea</t>
+  </si>
+  <si>
+    <t>Verkaufspreiseanalyse</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis Bilanznull</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>Verkaufspreis Bilanznull mit Vorverkauf</t>
+  </si>
+  <si>
+    <t>calc_price</t>
   </si>
 </sst>
 </file>
@@ -3213,7 +3228,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
@@ -4813,7 +4828,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="46"/>
+      <c r="A119" s="48"/>
       <c r="B119" s="54"/>
       <c r="C119" s="1" t="s">
         <v>175</v>
@@ -4826,7 +4841,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="46"/>
+      <c r="A120" s="48"/>
       <c r="B120" s="58"/>
       <c r="C120" s="13"/>
       <c r="D120" s="13"/>
@@ -4834,7 +4849,7 @@
       <c r="F120" s="13"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="46"/>
+      <c r="A121" s="48"/>
       <c r="B121" s="57" t="s">
         <v>184</v>
       </c>
@@ -4849,7 +4864,7 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="46"/>
+      <c r="A122" s="48"/>
       <c r="B122" s="54"/>
       <c r="C122" s="1" t="s">
         <v>182</v>
@@ -4862,7 +4877,7 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="46"/>
+      <c r="A123" s="48"/>
       <c r="B123" s="54"/>
       <c r="C123" s="1" t="s">
         <v>178</v>
@@ -4875,7 +4890,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="46"/>
+      <c r="A124" s="48"/>
       <c r="B124" s="54"/>
       <c r="C124" s="1" t="s">
         <v>180</v>
@@ -4888,7 +4903,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="46"/>
+      <c r="A125" s="48"/>
       <c r="B125" s="54"/>
       <c r="C125" s="1" t="s">
         <v>183</v>
@@ -4901,7 +4916,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="46"/>
+      <c r="A126" s="48"/>
       <c r="B126" s="54"/>
       <c r="C126" s="1" t="s">
         <v>193</v>
@@ -4914,11 +4929,11 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="46"/>
+      <c r="A127" s="48"/>
       <c r="B127" s="54"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="46"/>
+      <c r="A128" s="48"/>
       <c r="B128" s="57" t="s">
         <v>208</v>
       </c>
@@ -4934,7 +4949,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="46"/>
+      <c r="A129" s="48"/>
       <c r="B129" s="54"/>
       <c r="C129" s="1" t="s">
         <v>206</v>
@@ -4947,7 +4962,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="46"/>
+      <c r="A130" s="48"/>
       <c r="B130" s="54"/>
       <c r="C130" s="1" t="s">
         <v>217</v>
@@ -4960,7 +4975,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="46"/>
+      <c r="A131" s="48"/>
       <c r="B131" s="54"/>
       <c r="C131" s="1" t="s">
         <v>207</v>
@@ -4973,7 +4988,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="46"/>
+      <c r="A132" s="48"/>
       <c r="B132" s="54"/>
       <c r="C132" s="1" t="s">
         <v>312</v>
@@ -4986,7 +5001,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="46"/>
+      <c r="A133" s="48"/>
       <c r="B133" s="54"/>
       <c r="C133" s="1" t="s">
         <v>336</v>
@@ -4999,7 +5014,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="46"/>
+      <c r="A134" s="48"/>
       <c r="B134" s="54"/>
       <c r="C134" s="1" t="s">
         <v>338</v>
@@ -5012,7 +5027,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="46"/>
+      <c r="A135" s="48"/>
       <c r="B135" s="54"/>
       <c r="C135" s="1" t="s">
         <v>219</v>
@@ -5025,7 +5040,7 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="46"/>
+      <c r="A136" s="48"/>
       <c r="B136" s="54"/>
       <c r="C136" s="1" t="s">
         <v>223</v>
@@ -5038,7 +5053,7 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="46"/>
+      <c r="A137" s="48"/>
       <c r="B137" s="54"/>
       <c r="C137" s="1" t="s">
         <v>204</v>
@@ -5051,7 +5066,7 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="46"/>
+      <c r="A138" s="48"/>
       <c r="B138" s="54"/>
       <c r="C138" s="1" t="s">
         <v>266</v>
@@ -5064,7 +5079,7 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="46"/>
+      <c r="A139" s="48"/>
       <c r="B139" s="54"/>
       <c r="C139" s="1" t="s">
         <v>268</v>
@@ -5077,11 +5092,11 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="46"/>
+      <c r="A140" s="48"/>
       <c r="B140" s="54"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="46"/>
+      <c r="A141" s="48"/>
       <c r="B141" s="57" t="s">
         <v>224</v>
       </c>
@@ -5097,8 +5112,8 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="46"/>
-      <c r="B142" s="54"/>
+      <c r="A142" s="48"/>
+      <c r="B142" s="60"/>
       <c r="C142" s="1" t="s">
         <v>314</v>
       </c>
@@ -5110,8 +5125,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="46"/>
-      <c r="B143" s="54"/>
+      <c r="A143" s="48"/>
+      <c r="B143" s="60"/>
       <c r="C143" s="1" t="s">
         <v>227</v>
       </c>
@@ -5123,8 +5138,8 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="46"/>
-      <c r="B144" s="54"/>
+      <c r="A144" s="48"/>
+      <c r="B144" s="60"/>
       <c r="C144" s="1" t="s">
         <v>269</v>
       </c>
@@ -5136,8 +5151,8 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="46"/>
-      <c r="B145" s="54"/>
+      <c r="A145" s="48"/>
+      <c r="B145" s="60"/>
       <c r="C145" s="1" t="s">
         <v>271</v>
       </c>
@@ -5148,13 +5163,59 @@
         <v>215</v>
       </c>
     </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="48"/>
+      <c r="B146" s="58"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="48"/>
+      <c r="B147" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="48"/>
+      <c r="B148" s="54"/>
+      <c r="C148" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="48"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="A118:A149"/>
+    <mergeCell ref="A2:A45"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B45"/>
+    <mergeCell ref="A46:A77"/>
+    <mergeCell ref="B66:B77"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="B56:B65"/>
     <mergeCell ref="B81:B83"/>
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
-    <mergeCell ref="B141:B145"/>
-    <mergeCell ref="A118:A145"/>
     <mergeCell ref="B128:B140"/>
     <mergeCell ref="B118:B120"/>
     <mergeCell ref="A78:A103"/>
@@ -5165,15 +5226,6 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B111"/>
     <mergeCell ref="B78:B80"/>
-    <mergeCell ref="A2:A45"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B45"/>
-    <mergeCell ref="A46:A77"/>
-    <mergeCell ref="B66:B77"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="B56:B65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
+++ b/Methanol/Methanol_Brownfield_Memmingen_Bio/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDE88E2-6357-429F-8770-CEB1ACFB89C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB321755-11A9-4296-B9D2-67D4CB6B7F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="388">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1333,6 +1333,9 @@
   </si>
   <si>
     <t>calc_price</t>
+  </si>
+  <si>
+    <t>kWh_th/a</t>
   </si>
 </sst>
 </file>
@@ -3165,7 +3168,7 @@
         <v>-1E-4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -4035,7 +4038,7 @@
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="1" t="s">
-        <v>133</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4049,7 +4052,7 @@
       </c>
       <c r="E59" s="9"/>
       <c r="F59" s="1" t="s">
-        <v>133</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -5201,6 +5204,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5217,15 +5229,6 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
